--- a/data_lake/industry/TrendForce/Li-Ion Battery.xlsx
+++ b/data_lake/industry/TrendForce/Li-Ion Battery.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data_lake/industry/TrendForce/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/industry/TrendForce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A7A542-2468-534C-BAFE-5388455D0484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7C197B8-EBE4-F54E-B037-6CF058DD1781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22160" yWindow="600" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16960" yWindow="780" windowWidth="19040" windowHeight="20860" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Battery Cell &amp; Pack" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="71">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -746,7 +746,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="9" bestFit="1" customWidth="1"/>
@@ -1097,6 +1097,41 @@
         <v>0.51</v>
       </c>
     </row>
+    <row r="10" spans="1:21">
+      <c r="A10" s="9">
+        <v>46272</v>
+      </c>
+      <c r="B10" s="9">
+        <v>46272</v>
+      </c>
+      <c r="C10" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="14">
+        <v>0.62</v>
+      </c>
+      <c r="F10" s="14">
+        <v>0.4</v>
+      </c>
+      <c r="G10" s="14">
+        <v>0.63</v>
+      </c>
+      <c r="H10" s="14">
+        <v>0.38</v>
+      </c>
+      <c r="I10" s="14">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="J10" s="14">
+        <v>0.79</v>
+      </c>
+      <c r="K10" s="14">
+        <v>0.52</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1106,7 +1141,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F93A7413-903B-41E3-BDE3-CD88FC030C93}">
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="9" bestFit="1" customWidth="1"/>
@@ -1530,6 +1565,50 @@
         <v>5.76</v>
       </c>
     </row>
+    <row r="10" spans="1:21">
+      <c r="A10" s="9">
+        <v>46272</v>
+      </c>
+      <c r="B10" s="9">
+        <v>46272</v>
+      </c>
+      <c r="C10" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="14">
+        <v>1.58</v>
+      </c>
+      <c r="F10" s="14">
+        <v>9.51</v>
+      </c>
+      <c r="G10" s="14">
+        <v>9.4</v>
+      </c>
+      <c r="H10" s="14">
+        <v>11.14</v>
+      </c>
+      <c r="I10" s="14">
+        <v>17.18</v>
+      </c>
+      <c r="J10" s="14">
+        <v>17.75</v>
+      </c>
+      <c r="K10" s="14">
+        <v>19.68</v>
+      </c>
+      <c r="L10" s="14">
+        <v>5.65</v>
+      </c>
+      <c r="M10" s="14">
+        <v>33.909999999999997</v>
+      </c>
+      <c r="N10" s="14">
+        <v>5.51</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1538,7 +1617,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0866DC8-FCF3-4C5E-83C2-1F3B814AC134}">
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="9" bestFit="1" customWidth="1"/>
@@ -1913,6 +1992,44 @@
         <v>5.2</v>
       </c>
     </row>
+    <row r="10" spans="1:21">
+      <c r="A10" s="9">
+        <v>46272</v>
+      </c>
+      <c r="B10" s="9">
+        <v>46272</v>
+      </c>
+      <c r="C10" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="14">
+        <v>0.85</v>
+      </c>
+      <c r="F10" s="14">
+        <v>1.02</v>
+      </c>
+      <c r="G10" s="14">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="H10" s="14">
+        <v>2.94</v>
+      </c>
+      <c r="I10" s="14">
+        <v>4.84</v>
+      </c>
+      <c r="J10" s="14">
+        <v>2.13</v>
+      </c>
+      <c r="K10" s="14">
+        <v>2.89</v>
+      </c>
+      <c r="L10" s="14">
+        <v>5.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1921,7 +2038,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE236D12-0519-456D-89C0-C829EF6FE190}">
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="9" bestFit="1" customWidth="1"/>
@@ -2224,6 +2341,35 @@
         <v>1.18</v>
       </c>
     </row>
+    <row r="10" spans="1:21">
+      <c r="A10" s="9">
+        <v>46272</v>
+      </c>
+      <c r="B10" s="9">
+        <v>46272</v>
+      </c>
+      <c r="C10" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="14">
+        <v>0.45</v>
+      </c>
+      <c r="F10" s="14">
+        <v>0.9</v>
+      </c>
+      <c r="G10" s="14">
+        <v>0.88</v>
+      </c>
+      <c r="H10" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="I10" s="14">
+        <v>1.18</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2232,7 +2378,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B864B0A-C2A5-4EA0-8D10-4C40685755EC}">
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.1640625" style="9" bestFit="1" customWidth="1"/>
@@ -2511,6 +2657,32 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
+    <row r="10" spans="1:21">
+      <c r="A10" s="9">
+        <v>46272</v>
+      </c>
+      <c r="B10" s="9">
+        <v>46272</v>
+      </c>
+      <c r="C10" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="14">
+        <v>10.86</v>
+      </c>
+      <c r="F10" s="14">
+        <v>3.2</v>
+      </c>
+      <c r="G10" s="14">
+        <v>3.1</v>
+      </c>
+      <c r="H10" s="14">
+        <v>4.55</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2519,7 +2691,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F64F3CCF-5660-444E-BF2D-168013FA393D}">
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.1640625" style="9" bestFit="1" customWidth="1"/>
@@ -2895,6 +3067,44 @@
         <v>3.25</v>
       </c>
     </row>
+    <row r="10" spans="1:21">
+      <c r="A10" s="9">
+        <v>46272</v>
+      </c>
+      <c r="B10" s="9">
+        <v>46272</v>
+      </c>
+      <c r="C10" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="16">
+        <v>2158</v>
+      </c>
+      <c r="F10" s="14">
+        <v>14.99</v>
+      </c>
+      <c r="G10" s="14">
+        <v>14.16</v>
+      </c>
+      <c r="H10" s="14">
+        <v>32.06</v>
+      </c>
+      <c r="I10" s="14">
+        <v>28.75</v>
+      </c>
+      <c r="J10" s="14">
+        <v>7.77</v>
+      </c>
+      <c r="K10" s="14">
+        <v>13.07</v>
+      </c>
+      <c r="L10" s="14">
+        <v>3.15</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2903,7 +3113,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC9B3F37-91A5-425D-8E2F-CBD919F64D9B}">
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.1640625" style="9" bestFit="1" customWidth="1"/>
@@ -3132,6 +3342,26 @@
         <v>2.1</v>
       </c>
       <c r="F9" s="14">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
+      <c r="A10" s="9">
+        <v>46272</v>
+      </c>
+      <c r="B10" s="9">
+        <v>46272</v>
+      </c>
+      <c r="C10" s="10">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="14">
+        <v>2.15</v>
+      </c>
+      <c r="F10" s="14">
         <v>1.6</v>
       </c>
     </row>
